--- a/knowledge/shared/templates/raw/AcuRev-1300_v1.01_20260416.xlsx
+++ b/knowledge/shared/templates/raw/AcuRev-1300_v1.01_20260416.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://accuenergycom.sharepoint.com/sites/CN-Project-AcuHMI/Shared Documents/PX-EMD-G/13 项目各领域交付件/06 PM(产品)/02 商业需求规格书/参数类区分/模板管理/AcuRev-1300&amp;PXM350/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{FD164DB1-B618-42E6-B24A-20BF35C8B086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E95389-B0B2-49D2-9166-622913F8485C}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:1_{FD164DB1-B618-42E6-B24A-20BF35C8B086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63839B42-8D08-47F0-A8E1-97B7786E0455}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,13 +42,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="255">
   <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>blockId</t>
-  </si>
-  <si>
-    <t>isOnline</t>
-  </si>
-  <si>
-    <t>ID</t>
   </si>
   <si>
     <t>paramId</t>
@@ -91,6 +88,14 @@
     <t>Alarm</t>
   </si>
   <si>
+    <t>Data log default parameter</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trend Log</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>DataLog</t>
   </si>
   <si>
@@ -117,6 +122,9 @@
     <t>IsOnline</t>
   </si>
   <si>
+    <t>isOnline</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -446,382 +454,374 @@
     <t>Phase C Export Active Energy</t>
   </si>
   <si>
+    <t>EP_EXP_c_kWh</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>2-5</t>
   </si>
   <si>
     <t>System Import Active Energy</t>
-  </si>
-  <si>
-    <t>2-6</t>
-  </si>
-  <si>
-    <t>Phase A Import Active Energy</t>
-  </si>
-  <si>
-    <t>EP_IMP_a_kWh</t>
-  </si>
-  <si>
-    <t>2-7</t>
-  </si>
-  <si>
-    <t>Phase B Import Active Energy</t>
-  </si>
-  <si>
-    <t>EP_IMP_b_kWh</t>
-  </si>
-  <si>
-    <t>2-8</t>
-  </si>
-  <si>
-    <t>Phase C Import Active Energy</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>System Active Power Demand</t>
-  </si>
-  <si>
-    <t>DMD_P_kW</t>
-  </si>
-  <si>
-    <t>demand</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>System Reactive Power Demand</t>
-  </si>
-  <si>
-    <t>DMD_Q_kvar</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>System Apparent Power Demand</t>
-  </si>
-  <si>
-    <t>DMD_S_kVA</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>Communication Address</t>
-  </si>
-  <si>
-    <t>Conf_Ch1_Addr</t>
-  </si>
-  <si>
-    <t>uint16</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>RS485 Communication Baud Rate</t>
-  </si>
-  <si>
-    <t>Conf_Ch1_Baud</t>
-  </si>
-  <si>
-    <t>4-3</t>
-  </si>
-  <si>
-    <t>RS485 Communication Parity</t>
-  </si>
-  <si>
-    <t>Conf_Ch1_Parity</t>
-  </si>
-  <si>
-    <t>4-4</t>
-  </si>
-  <si>
-    <t>Pulse Parameter</t>
-  </si>
-  <si>
-    <t>Conf_PulseParam</t>
-  </si>
-  <si>
-    <t>4-5</t>
-  </si>
-  <si>
-    <t>Demand Method</t>
-  </si>
-  <si>
-    <t>Conf_Dmd_Method</t>
-  </si>
-  <si>
-    <t>4-6</t>
-  </si>
-  <si>
-    <t>Demand Window</t>
-  </si>
-  <si>
-    <t>Conf_Dmd_Window</t>
-  </si>
-  <si>
-    <t>4-7</t>
-  </si>
-  <si>
-    <t>Demand Sub Interval</t>
-  </si>
-  <si>
-    <t>Conf_Dmd_SubInterval</t>
-  </si>
-  <si>
-    <t>4-8</t>
-  </si>
-  <si>
-    <t>Reactive Power Calculation Method</t>
-  </si>
-  <si>
-    <t>Conf_CalcMethod_Q</t>
-  </si>
-  <si>
-    <t>4-9</t>
-  </si>
-  <si>
-    <t>VAR/PF Convention</t>
-  </si>
-  <si>
-    <t>Conf_CalcMethod_VarPF</t>
-  </si>
-  <si>
-    <t>4-10</t>
-  </si>
-  <si>
-    <t>Non-standard content seal option</t>
-  </si>
-  <si>
-    <t>Conf_Seal_Option</t>
-  </si>
-  <si>
-    <t>4-11</t>
-  </si>
-  <si>
-    <t>Communication Permission</t>
-  </si>
-  <si>
-    <t>Conf_Comm_Perm</t>
-  </si>
-  <si>
-    <t>4-12</t>
-  </si>
-  <si>
-    <t>Current Password</t>
-  </si>
-  <si>
-    <t>Conf_Curr_Pwd</t>
-  </si>
-  <si>
-    <t>4-13</t>
-  </si>
-  <si>
-    <t>New Password</t>
-  </si>
-  <si>
-    <t>Conf_New_Pwd</t>
-  </si>
-  <si>
-    <t>4-14</t>
-  </si>
-  <si>
-    <t>Clear Meter Data</t>
-  </si>
-  <si>
-    <t>Conf_Clr_Data</t>
-  </si>
-  <si>
-    <t>4-15</t>
-  </si>
-  <si>
-    <t>Optional Display Flag Word 1</t>
-  </si>
-  <si>
-    <t>Conf_OptWord1</t>
-  </si>
-  <si>
-    <t>4-16</t>
-  </si>
-  <si>
-    <t>Optional Display Flag Word 2</t>
-  </si>
-  <si>
-    <t>Conf_OptWord2</t>
-  </si>
-  <si>
-    <t>4-17</t>
-  </si>
-  <si>
-    <t>Basic Reading Display Primary/Secondary</t>
-  </si>
-  <si>
-    <t>Conf_DispFormat_RealTime</t>
-  </si>
-  <si>
-    <t>4-18</t>
-  </si>
-  <si>
-    <t>Service Configuration</t>
-  </si>
-  <si>
-    <t>Conf_ServiceConfig</t>
-  </si>
-  <si>
-    <t>4-19</t>
-  </si>
-  <si>
-    <t>CT2 Value</t>
-  </si>
-  <si>
-    <t>Conf_CT2</t>
-  </si>
-  <si>
-    <t>4-20</t>
-  </si>
-  <si>
-    <t>CT1 Value</t>
-  </si>
-  <si>
-    <t>Conf_CT1</t>
-  </si>
-  <si>
-    <t>4-21</t>
-  </si>
-  <si>
-    <t>CTN Value</t>
-  </si>
-  <si>
-    <t>Conf_CT41</t>
-  </si>
-  <si>
-    <t>4-22</t>
-  </si>
-  <si>
-    <t>PT2</t>
-  </si>
-  <si>
-    <t>Conf_PT2</t>
-  </si>
-  <si>
-    <t>4-23</t>
-  </si>
-  <si>
-    <t>PT1</t>
-  </si>
-  <si>
-    <t>Conf_PT1</t>
-  </si>
-  <si>
-    <t>4-24</t>
-  </si>
-  <si>
-    <t>Pulse Constant</t>
-  </si>
-  <si>
-    <t>Conf_PulseConst</t>
-  </si>
-  <si>
-    <t>4-25</t>
-  </si>
-  <si>
-    <t>Pulse Width</t>
-  </si>
-  <si>
-    <t>Conf_PulseWidth</t>
-  </si>
-  <si>
-    <t>4-26</t>
-  </si>
-  <si>
-    <t>Energy Display Decimal Digits</t>
-  </si>
-  <si>
-    <t>Conf_Energy_Digits</t>
-  </si>
-  <si>
-    <t>4-27</t>
-  </si>
-  <si>
-    <t>RO Output Mode</t>
-  </si>
-  <si>
-    <t>Conf_RO_Mode</t>
-  </si>
-  <si>
-    <t>4-28</t>
-  </si>
-  <si>
-    <t>Enable Wiring Error Detection</t>
-  </si>
-  <si>
-    <t>Conf_Enable_Detect_WireError</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>Wiring Error</t>
-  </si>
-  <si>
-    <t>Info_WireError</t>
-  </si>
-  <si>
-    <t>5-2</t>
-  </si>
-  <si>
-    <t>Sealing status</t>
-  </si>
-  <si>
-    <t>Info_Seal_Status</t>
-  </si>
-  <si>
-    <t>5-3</t>
-  </si>
-  <si>
-    <t>Enclosure status</t>
-  </si>
-  <si>
-    <t>Info_Enclosure_Status</t>
-  </si>
-  <si>
-    <t>6-1</t>
-  </si>
-  <si>
-    <t>InfoCT2Type</t>
-  </si>
-  <si>
-    <t>Info_CT2_Type</t>
-  </si>
-  <si>
-    <t>Data log default parameter</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Trend Log</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>EP_IMP_kWh</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>2-6</t>
+  </si>
+  <si>
+    <t>Phase A Import Active Energy</t>
+  </si>
+  <si>
+    <t>EP_IMP_a_kWh</t>
+  </si>
+  <si>
+    <t>2-7</t>
+  </si>
+  <si>
+    <t>Phase B Import Active Energy</t>
+  </si>
+  <si>
+    <t>EP_IMP_b_kWh</t>
+  </si>
+  <si>
+    <t>2-8</t>
+  </si>
+  <si>
+    <t>Phase C Import Active Energy</t>
+  </si>
+  <si>
     <t>EP_IMP_c_kWh</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>EP_EXP_c_kWh</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>System Active Power Demand</t>
+  </si>
+  <si>
+    <t>DMD_P_kW</t>
+  </si>
+  <si>
+    <t>demand</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>System Reactive Power Demand</t>
+  </si>
+  <si>
+    <t>DMD_Q_kvar</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>System Apparent Power Demand</t>
+  </si>
+  <si>
+    <t>DMD_S_kVA</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>Communication Address</t>
+  </si>
+  <si>
+    <t>Conf_Ch1_Addr</t>
+  </si>
+  <si>
+    <t>uint16</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>RS485 Communication Baud Rate</t>
+  </si>
+  <si>
+    <t>Conf_Ch1_Baud</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>RS485 Communication Parity</t>
+  </si>
+  <si>
+    <t>Conf_Ch1_Parity</t>
+  </si>
+  <si>
+    <t>4-4</t>
+  </si>
+  <si>
+    <t>Pulse Parameter</t>
+  </si>
+  <si>
+    <t>Conf_PulseParam</t>
+  </si>
+  <si>
+    <t>4-5</t>
+  </si>
+  <si>
+    <t>Demand Method</t>
+  </si>
+  <si>
+    <t>Conf_Dmd_Method</t>
+  </si>
+  <si>
+    <t>4-6</t>
+  </si>
+  <si>
+    <t>Demand Window</t>
+  </si>
+  <si>
+    <t>Conf_Dmd_Window</t>
+  </si>
+  <si>
+    <t>4-7</t>
+  </si>
+  <si>
+    <t>Demand Sub Interval</t>
+  </si>
+  <si>
+    <t>Conf_Dmd_SubInterval</t>
+  </si>
+  <si>
+    <t>4-8</t>
+  </si>
+  <si>
+    <t>Reactive Power Calculation Method</t>
+  </si>
+  <si>
+    <t>Conf_CalcMethod_Q</t>
+  </si>
+  <si>
+    <t>4-9</t>
+  </si>
+  <si>
+    <t>VAR/PF Convention</t>
+  </si>
+  <si>
+    <t>Conf_CalcMethod_VarPF</t>
+  </si>
+  <si>
+    <t>4-10</t>
+  </si>
+  <si>
+    <t>Non-standard content seal option</t>
+  </si>
+  <si>
+    <t>Conf_Seal_Option</t>
+  </si>
+  <si>
+    <t>4-11</t>
+  </si>
+  <si>
+    <t>Communication Permission</t>
+  </si>
+  <si>
+    <t>Conf_Comm_Perm</t>
+  </si>
+  <si>
+    <t>4-12</t>
+  </si>
+  <si>
+    <t>Current Password</t>
+  </si>
+  <si>
+    <t>Conf_Curr_Pwd</t>
+  </si>
+  <si>
+    <t>4-13</t>
+  </si>
+  <si>
+    <t>New Password</t>
+  </si>
+  <si>
+    <t>Conf_New_Pwd</t>
+  </si>
+  <si>
+    <t>4-14</t>
+  </si>
+  <si>
+    <t>Clear Meter Data</t>
+  </si>
+  <si>
+    <t>Conf_Clr_Data</t>
+  </si>
+  <si>
+    <t>4-15</t>
+  </si>
+  <si>
+    <t>Optional Display Flag Word 1</t>
+  </si>
+  <si>
+    <t>Conf_OptWord1</t>
+  </si>
+  <si>
+    <t>4-16</t>
+  </si>
+  <si>
+    <t>Optional Display Flag Word 2</t>
+  </si>
+  <si>
+    <t>Conf_OptWord2</t>
+  </si>
+  <si>
+    <t>4-17</t>
+  </si>
+  <si>
+    <t>Basic Reading Display Primary/Secondary</t>
+  </si>
+  <si>
+    <t>Conf_DispFormat_RealTime</t>
+  </si>
+  <si>
+    <t>4-18</t>
+  </si>
+  <si>
+    <t>Service Configuration</t>
+  </si>
+  <si>
+    <t>Conf_ServiceConfig</t>
+  </si>
+  <si>
+    <t>4-19</t>
+  </si>
+  <si>
+    <t>CT2 Value</t>
+  </si>
+  <si>
+    <t>Conf_CT2</t>
+  </si>
+  <si>
+    <t>4-20</t>
+  </si>
+  <si>
+    <t>CT1 Value</t>
+  </si>
+  <si>
+    <t>Conf_CT1</t>
+  </si>
+  <si>
+    <t>4-21</t>
+  </si>
+  <si>
+    <t>CTN Value</t>
+  </si>
+  <si>
+    <t>Conf_CT41</t>
+  </si>
+  <si>
+    <t>4-22</t>
+  </si>
+  <si>
+    <t>PT2</t>
+  </si>
+  <si>
+    <t>Conf_PT2</t>
+  </si>
+  <si>
+    <t>4-23</t>
+  </si>
+  <si>
+    <t>PT1</t>
+  </si>
+  <si>
+    <t>Conf_PT1</t>
+  </si>
+  <si>
+    <t>4-24</t>
+  </si>
+  <si>
+    <t>Pulse Constant</t>
+  </si>
+  <si>
+    <t>Conf_PulseConst</t>
+  </si>
+  <si>
+    <t>4-25</t>
+  </si>
+  <si>
+    <t>Pulse Width</t>
+  </si>
+  <si>
+    <t>Conf_PulseWidth</t>
+  </si>
+  <si>
+    <t>4-26</t>
+  </si>
+  <si>
+    <t>Energy Display Decimal Digits</t>
+  </si>
+  <si>
+    <t>Conf_Energy_Digits</t>
+  </si>
+  <si>
+    <t>4-27</t>
+  </si>
+  <si>
+    <t>RO Output Mode</t>
+  </si>
+  <si>
+    <t>Conf_RO_Mode</t>
+  </si>
+  <si>
+    <t>4-28</t>
+  </si>
+  <si>
+    <t>Enable Wiring Error Detection</t>
+  </si>
+  <si>
+    <t>Conf_Enable_Detect_WireError</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>Wiring Error</t>
+  </si>
+  <si>
+    <t>Info_WireError</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>Sealing status</t>
+  </si>
+  <si>
+    <t>Info_Seal_Status</t>
+  </si>
+  <si>
+    <t>5-3</t>
+  </si>
+  <si>
+    <t>Enclosure status</t>
+  </si>
+  <si>
+    <t>Info_Enclosure_Status</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>InfoCT2Type</t>
+  </si>
+  <si>
+    <t>Info_CT2_Type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1351,105 +1351,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AB73"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X73"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="7.21875" style="5" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" style="28" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" style="31" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="29" customWidth="1"/>
-    <col min="12" max="12" width="9.21875" style="6" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="29" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" style="5" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5546875" customWidth="1"/>
-    <col min="17" max="17" width="24.33203125" customWidth="1"/>
-    <col min="18" max="23" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.625" style="5" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="7.25" style="5" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="28" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="31" customWidth="1"/>
+    <col min="10" max="10" width="13.625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="13.625" style="29" customWidth="1"/>
+    <col min="12" max="12" width="9.25" style="6" customWidth="1"/>
+    <col min="13" max="13" width="9.5" style="29" customWidth="1"/>
+    <col min="14" max="14" width="10.625" style="5" customWidth="1"/>
+    <col min="15" max="15" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.875" customWidth="1"/>
+    <col min="17" max="17" width="24.375" customWidth="1"/>
+    <col min="18" max="23" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="18.75" customHeight="1">
       <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="10" t="s">
-        <v>12</v>
-      </c>
       <c r="M1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="4" t="s">
-        <v>250</v>
-      </c>
       <c r="Q1" s="4" t="s">
-        <v>251</v>
+        <v>16</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="4"/>
     </row>
-    <row r="2" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="18.75" customHeight="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="12">
         <v>0</v>
@@ -1466,21 +1466,21 @@
         <v>0</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="14"/>
       <c r="J2" s="13" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K2" s="15">
         <v>1</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M2" s="15">
         <v>1</v>
@@ -1498,7 +1498,7 @@
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
     </row>
-    <row r="3" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="18.75" customHeight="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="12">
         <f t="shared" ref="D3:D30" si="0">E3-8194</f>
@@ -1516,23 +1516,23 @@
         <v>8194</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K3" s="15">
         <v>12</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M3" s="15">
         <v>2</v>
@@ -1541,37 +1541,37 @@
         <v>1</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="18.75" customHeight="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" s="12">
         <f t="shared" si="0"/>
@@ -1590,23 +1590,23 @@
         <v>8196</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K4" s="15">
         <v>12</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M4" s="15">
         <v>2</v>
@@ -1615,37 +1615,37 @@
         <v>1</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="18.75" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="12">
         <f t="shared" si="0"/>
@@ -1664,23 +1664,23 @@
         <v>8198</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K5" s="15">
         <v>12</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M5" s="15">
         <v>2</v>
@@ -1689,37 +1689,37 @@
         <v>1</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="18.75" customHeight="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="12">
         <f t="shared" si="0"/>
@@ -1738,23 +1738,23 @@
         <v>8200</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K6" s="15">
         <v>12</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M6" s="15">
         <v>2</v>
@@ -1763,37 +1763,37 @@
         <v>1</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="18.75" customHeight="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" s="12">
         <f t="shared" si="0"/>
@@ -1812,23 +1812,23 @@
         <v>8202</v>
       </c>
       <c r="F7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K7" s="15">
         <v>12</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M7" s="15">
         <v>2</v>
@@ -1837,37 +1837,37 @@
         <v>1</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="18.75" customHeight="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="12">
         <f t="shared" si="0"/>
@@ -1886,23 +1886,23 @@
         <v>8204</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K8" s="15">
         <v>12</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M8" s="15">
         <v>2</v>
@@ -1911,37 +1911,37 @@
         <v>1</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="18.75" customHeight="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" s="12">
         <f t="shared" si="0"/>
@@ -1960,23 +1960,23 @@
         <v>8206</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K9" s="15">
         <v>12</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M9" s="15">
         <v>2</v>
@@ -1985,37 +1985,37 @@
         <v>1</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="18.75" customHeight="1">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10" s="12">
         <f t="shared" si="0"/>
@@ -2034,23 +2034,23 @@
         <v>8208</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K10" s="15">
         <v>12</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M10" s="15">
         <v>2</v>
@@ -2059,37 +2059,37 @@
         <v>1</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="18.75" customHeight="1">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11" s="12">
         <f t="shared" si="0"/>
@@ -2108,23 +2108,23 @@
         <v>8210</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K11" s="15">
         <v>12</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M11" s="15">
         <v>2</v>
@@ -2133,37 +2133,37 @@
         <v>1</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="18.75" customHeight="1">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12" s="12">
         <f t="shared" si="0"/>
@@ -2182,23 +2182,23 @@
         <v>8212</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K12" s="15">
         <v>12</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M12" s="15">
         <v>2</v>
@@ -2207,37 +2207,37 @@
         <v>1</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="18.75" customHeight="1">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" s="12">
         <f t="shared" si="0"/>
@@ -2256,23 +2256,23 @@
         <v>8214</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K13" s="15">
         <v>12</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M13" s="15">
         <v>2</v>
@@ -2281,37 +2281,37 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="18.75" customHeight="1">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" s="12">
         <f t="shared" si="0"/>
@@ -2330,23 +2330,23 @@
         <v>8216</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K14" s="15">
         <v>12</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M14" s="15">
         <v>2</v>
@@ -2355,37 +2355,37 @@
         <v>1</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="18.75" customHeight="1">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" s="12">
         <f t="shared" si="0"/>
@@ -2404,23 +2404,23 @@
         <v>8218</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K15" s="15">
         <v>12</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M15" s="15">
         <v>2</v>
@@ -2429,37 +2429,37 @@
         <v>1E-3</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="18.75" customHeight="1">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" s="12">
         <f t="shared" si="0"/>
@@ -2478,23 +2478,23 @@
         <v>8220</v>
       </c>
       <c r="F16" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K16" s="15">
         <v>12</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M16" s="15">
         <v>2</v>
@@ -2503,37 +2503,37 @@
         <v>1E-3</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="18.75" customHeight="1">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D17" s="12">
         <f t="shared" si="0"/>
@@ -2552,23 +2552,23 @@
         <v>8222</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K17" s="15">
         <v>12</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M17" s="15">
         <v>2</v>
@@ -2577,37 +2577,37 @@
         <v>1E-3</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="18.75" customHeight="1">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D18" s="12">
         <f t="shared" si="0"/>
@@ -2626,23 +2626,23 @@
         <v>8224</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
         <v>12</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M18" s="15">
         <v>2</v>
@@ -2651,37 +2651,37 @@
         <v>1E-3</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="18.75" customHeight="1">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D19" s="12">
         <f t="shared" si="0"/>
@@ -2700,23 +2700,23 @@
         <v>8226</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K19" s="15">
         <v>12</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M19" s="15">
         <v>2</v>
@@ -2725,37 +2725,37 @@
         <v>1E-3</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="18.75" customHeight="1">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D20" s="12">
         <f t="shared" si="0"/>
@@ -2774,23 +2774,23 @@
         <v>8228</v>
       </c>
       <c r="F20" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="13" t="s">
         <v>84</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>82</v>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
         <v>12</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M20" s="15">
         <v>2</v>
@@ -2799,37 +2799,37 @@
         <v>1E-3</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="18.75" customHeight="1">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D21" s="12">
         <f t="shared" si="0"/>
@@ -2848,23 +2848,23 @@
         <v>8230</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K21" s="15">
         <v>12</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M21" s="15">
         <v>2</v>
@@ -2873,37 +2873,37 @@
         <v>1E-3</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="18.75" customHeight="1">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D22" s="12">
         <f t="shared" si="0"/>
@@ -2922,23 +2922,23 @@
         <v>8232</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K22" s="15">
         <v>12</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M22" s="15">
         <v>2</v>
@@ -2947,37 +2947,37 @@
         <v>1E-3</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="18.75" customHeight="1">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D23" s="12">
         <f t="shared" si="0"/>
@@ -2996,23 +2996,23 @@
         <v>8234</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K23" s="15">
         <v>12</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M23" s="15">
         <v>2</v>
@@ -3021,37 +3021,37 @@
         <v>1E-3</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="18.75" customHeight="1">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D24" s="12">
         <f t="shared" si="0"/>
@@ -3070,23 +3070,23 @@
         <v>8236</v>
       </c>
       <c r="F24" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>95</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K24" s="15">
         <v>12</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M24" s="15">
         <v>2</v>
@@ -3095,37 +3095,37 @@
         <v>1E-3</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="18.75" customHeight="1">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D25" s="12">
         <f t="shared" si="0"/>
@@ -3144,23 +3144,23 @@
         <v>8238</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K25" s="15">
         <v>12</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M25" s="15">
         <v>2</v>
@@ -3169,37 +3169,37 @@
         <v>1E-3</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" ht="18.75" customHeight="1">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D26" s="12">
         <f t="shared" si="0"/>
@@ -3218,23 +3218,23 @@
         <v>8240</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K26" s="15">
         <v>12</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M26" s="15">
         <v>2</v>
@@ -3243,37 +3243,37 @@
         <v>1E-3</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="18.75" customHeight="1">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D27" s="12">
         <f t="shared" si="0"/>
@@ -3292,23 +3292,23 @@
         <v>8242</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H27" s="13"/>
       <c r="I27" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K27" s="15">
         <v>12</v>
       </c>
       <c r="L27" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M27" s="15">
         <v>2</v>
@@ -3317,35 +3317,35 @@
         <v>1</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="18.75" customHeight="1">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D28" s="12">
         <f t="shared" si="0"/>
@@ -3364,23 +3364,23 @@
         <v>8244</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K28" s="15">
         <v>12</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M28" s="15">
         <v>2</v>
@@ -3389,35 +3389,35 @@
         <v>1</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="18.75" customHeight="1">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D29" s="12">
         <f t="shared" si="0"/>
@@ -3436,23 +3436,23 @@
         <v>8246</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H29" s="13"/>
       <c r="I29" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K29" s="15">
         <v>12</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M29" s="15">
         <v>2</v>
@@ -3461,35 +3461,35 @@
         <v>1</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="18.75" customHeight="1">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" s="12">
         <f t="shared" si="0"/>
@@ -3508,23 +3508,23 @@
         <v>8248</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K30" s="15">
         <v>12</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M30" s="15">
         <v>2</v>
@@ -3533,35 +3533,35 @@
         <v>1</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="18.75" customHeight="1">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D31" s="12">
         <f t="shared" ref="D31:D38" si="2">E31-8262</f>
@@ -3579,23 +3579,23 @@
         <v>8262</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K31" s="15">
         <v>12</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M31" s="15">
         <v>2</v>
@@ -3604,34 +3604,34 @@
         <v>0.1</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="18.75" customHeight="1">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D32" s="12">
         <f t="shared" si="2"/>
@@ -3650,23 +3650,23 @@
         <v>8264</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K32" s="15">
         <v>12</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M32" s="15">
         <v>2</v>
@@ -3675,34 +3675,34 @@
         <v>0.1</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" ht="18.75" customHeight="1">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D33" s="12">
         <f t="shared" si="2"/>
@@ -3721,23 +3721,23 @@
         <v>8266</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K33" s="15">
         <v>12</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M33" s="15">
         <v>2</v>
@@ -3746,34 +3746,34 @@
         <v>0.1</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="18.75" customHeight="1">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D34" s="12">
         <f t="shared" si="2"/>
@@ -3792,23 +3792,23 @@
         <v>8268</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>254</v>
+        <v>135</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K34" s="15">
         <v>12</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M34" s="15">
         <v>2</v>
@@ -3817,34 +3817,34 @@
         <v>0.1</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" ht="18.75" customHeight="1">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D35" s="12">
         <f t="shared" si="2"/>
@@ -3863,23 +3863,23 @@
         <v>8270</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K35" s="15">
         <v>12</v>
       </c>
       <c r="L35" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M35" s="15">
         <v>2</v>
@@ -3888,34 +3888,34 @@
         <v>0.1</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="18.75" customHeight="1">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D36" s="12">
         <f t="shared" si="2"/>
@@ -3934,23 +3934,23 @@
         <v>8272</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K36" s="15">
         <v>12</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M36" s="15">
         <v>2</v>
@@ -3959,34 +3959,34 @@
         <v>0.1</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" ht="18.75" customHeight="1">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D37" s="12">
         <f t="shared" si="2"/>
@@ -4005,23 +4005,23 @@
         <v>8274</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K37" s="15">
         <v>12</v>
       </c>
       <c r="L37" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M37" s="15">
         <v>2</v>
@@ -4030,34 +4030,34 @@
         <v>0.1</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" ht="18.75" customHeight="1">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>2</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D38" s="12">
         <f t="shared" si="2"/>
@@ -4076,23 +4076,23 @@
         <v>8276</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>253</v>
+        <v>147</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K38" s="15">
         <v>12</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M38" s="15">
         <v>2</v>
@@ -4101,34 +4101,34 @@
         <v>0.1</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" ht="18.75" customHeight="1">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D39" s="12">
         <f>E39-4616</f>
@@ -4146,23 +4146,23 @@
         <v>4616</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K39" s="15">
         <v>12</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M39" s="15">
         <v>2</v>
@@ -4171,35 +4171,35 @@
         <v>1E-3</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="18.75" customHeight="1">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D40" s="12">
         <f>E40-4616</f>
@@ -4218,23 +4218,23 @@
         <v>4618</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K40" s="15">
         <v>12</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M40" s="15">
         <v>2</v>
@@ -4243,35 +4243,35 @@
         <v>1E-3</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" ht="18.75" customHeight="1">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D41" s="12">
         <f>E41-4616</f>
@@ -4290,23 +4290,23 @@
         <v>4620</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K41" s="15">
         <v>12</v>
       </c>
       <c r="L41" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M41" s="15">
         <v>2</v>
@@ -4315,35 +4315,35 @@
         <v>1E-3</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="18.75" customHeight="1">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D42" s="3">
         <v>0</v>
@@ -4360,19 +4360,19 @@
         <v>512</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K42" s="15">
         <v>12</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M42" s="15">
         <v>1</v>
@@ -4381,7 +4381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" ht="18.75" customHeight="1">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>4</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D43" s="3">
         <f t="shared" ref="D43:D69" si="4">E43-512</f>
@@ -4400,19 +4400,19 @@
         <v>513</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G43" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K43" s="15">
         <v>12</v>
       </c>
       <c r="L43" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M43" s="15">
         <v>1</v>
@@ -4421,7 +4421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" ht="18.75" customHeight="1">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>4</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D44" s="3">
         <f t="shared" si="4"/>
@@ -4440,19 +4440,19 @@
         <v>514</v>
       </c>
       <c r="F44" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G44" t="s">
+        <v>167</v>
+      </c>
+      <c r="J44" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="G44" t="s">
-        <v>162</v>
-      </c>
-      <c r="J44" s="13" t="s">
-        <v>156</v>
-      </c>
       <c r="K44" s="15">
         <v>12</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M44" s="15">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" ht="18.75" customHeight="1">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>4</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D45" s="3">
         <f t="shared" si="4"/>
@@ -4480,19 +4480,19 @@
         <v>515</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G45" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K45" s="15">
         <v>12</v>
       </c>
       <c r="L45" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M45" s="15">
         <v>1</v>
@@ -4501,7 +4501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" ht="18.75" customHeight="1">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>4</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D46" s="3">
         <f t="shared" si="4"/>
@@ -4520,19 +4520,19 @@
         <v>516</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G46" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K46" s="15">
         <v>12</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M46" s="15">
         <v>1</v>
@@ -4541,7 +4541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" ht="18.75" customHeight="1">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>4</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D47" s="3">
         <f t="shared" si="4"/>
@@ -4560,19 +4560,19 @@
         <v>517</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G47" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K47" s="15">
         <v>12</v>
       </c>
       <c r="L47" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M47" s="15">
         <v>1</v>
@@ -4581,7 +4581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" ht="18.75" customHeight="1">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -4589,7 +4589,7 @@
         <v>4</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="4"/>
@@ -4600,19 +4600,19 @@
         <v>518</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G48" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K48" s="15">
         <v>12</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M48" s="15">
         <v>1</v>
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="18.75" customHeight="1">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>4</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D49" s="3">
         <f t="shared" si="4"/>
@@ -4640,19 +4640,19 @@
         <v>519</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G49" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K49" s="15">
         <v>12</v>
       </c>
       <c r="L49" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M49" s="15">
         <v>1</v>
@@ -4661,7 +4661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="18.75" customHeight="1">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D50" s="3">
         <f t="shared" si="4"/>
@@ -4680,19 +4680,19 @@
         <v>520</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G50" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K50" s="15">
         <v>12</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M50" s="15">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="18.75" customHeight="1">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>4</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D51" s="3">
         <f t="shared" si="4"/>
@@ -4720,19 +4720,19 @@
         <v>521</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G51" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K51" s="15">
         <v>12</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M51" s="15">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="18.75" customHeight="1">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>4</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D52" s="3">
         <f t="shared" si="4"/>
@@ -4760,19 +4760,19 @@
         <v>522</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G52" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K52" s="15">
         <v>12</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M52" s="15">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="18.75" customHeight="1">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -4789,7 +4789,7 @@
         <v>4</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D53" s="3">
         <f t="shared" si="4"/>
@@ -4800,19 +4800,19 @@
         <v>523</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G53" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K53" s="15">
         <v>12</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M53" s="15">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="18.75" customHeight="1">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>4</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D54" s="3">
         <f t="shared" si="4"/>
@@ -4840,19 +4840,19 @@
         <v>524</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G54" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K54" s="15">
         <v>12</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M54" s="15">
         <v>1</v>
@@ -4861,7 +4861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="18.75" customHeight="1">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>4</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D55" s="3">
         <f t="shared" si="4"/>
@@ -4880,19 +4880,19 @@
         <v>525</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G55" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K55" s="15">
         <v>12</v>
       </c>
       <c r="L55" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M55" s="15">
         <v>1</v>
@@ -4901,7 +4901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="18.75" customHeight="1">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>4</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D56" s="3">
         <f t="shared" si="4"/>
@@ -4920,19 +4920,19 @@
         <v>526</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G56" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K56" s="15">
         <v>12</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M56" s="15">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="18.75" customHeight="1">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>4</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D57" s="3">
         <f t="shared" si="4"/>
@@ -4960,19 +4960,19 @@
         <v>527</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K57" s="15">
         <v>12</v>
       </c>
       <c r="L57" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M57" s="15">
         <v>1</v>
@@ -4981,7 +4981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="18.75" customHeight="1">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>4</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D58" s="3">
         <f t="shared" si="4"/>
@@ -5000,19 +5000,19 @@
         <v>528</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G58" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K58" s="15">
         <v>12</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M58" s="15">
         <v>1</v>
@@ -5021,7 +5021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="18.75" customHeight="1">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D59" s="3">
         <f t="shared" si="4"/>
@@ -5040,19 +5040,19 @@
         <v>529</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K59" s="15">
         <v>12</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M59" s="15">
         <v>1</v>
@@ -5061,7 +5061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="18.75" customHeight="1">
       <c r="A60" s="20">
         <v>59</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D60" s="20">
         <f t="shared" si="4"/>
@@ -5080,19 +5080,19 @@
         <v>530</v>
       </c>
       <c r="F60" s="23" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G60" s="24" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="J60" s="23" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K60" s="25">
         <v>12</v>
       </c>
       <c r="L60" s="23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M60" s="25">
         <v>1</v>
@@ -5101,7 +5101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="18.75" customHeight="1">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D61" s="3">
         <f t="shared" si="4"/>
@@ -5120,19 +5120,19 @@
         <v>531</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G61" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K61" s="15">
         <v>12</v>
       </c>
       <c r="L61" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M61" s="15">
         <v>1</v>
@@ -5141,7 +5141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="18.75" customHeight="1">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>4</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D62" s="3">
         <f t="shared" si="4"/>
@@ -5160,19 +5160,19 @@
         <v>532</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G62" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K62" s="15">
         <v>12</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M62" s="15">
         <v>1</v>
@@ -5181,7 +5181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="18.75" customHeight="1">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>4</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D63" s="3">
         <f t="shared" si="4"/>
@@ -5200,19 +5200,19 @@
         <v>533</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G63" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K63" s="15">
         <v>12</v>
       </c>
       <c r="L63" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M63" s="15">
         <v>1</v>
@@ -5221,7 +5221,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="18.75" customHeight="1">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -5229,7 +5229,7 @@
         <v>4</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D64" s="3">
         <f t="shared" si="4"/>
@@ -5240,19 +5240,19 @@
         <v>534</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G64" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="J64" s="23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K64" s="25">
         <v>12</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M64" s="25">
         <v>2</v>
@@ -5261,7 +5261,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="18.75" customHeight="1">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>4</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D65" s="3">
         <f t="shared" si="4"/>
@@ -5280,19 +5280,19 @@
         <v>536</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G65" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K65" s="15">
         <v>12</v>
       </c>
       <c r="L65" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M65" s="15">
         <v>1</v>
@@ -5301,7 +5301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" ht="18.75" customHeight="1">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>4</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D66" s="3">
         <f t="shared" si="4"/>
@@ -5320,19 +5320,19 @@
         <v>537</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G66" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K66" s="15">
         <v>12</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M66" s="15">
         <v>1</v>
@@ -5341,7 +5341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="18.75" customHeight="1">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>4</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D67" s="3">
         <f t="shared" si="4"/>
@@ -5360,19 +5360,19 @@
         <v>538</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G67" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K67" s="15">
         <v>12</v>
       </c>
       <c r="L67" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M67" s="15">
         <v>1</v>
@@ -5381,7 +5381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" ht="18.75" customHeight="1">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>4</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D68" s="3">
         <f t="shared" si="4"/>
@@ -5400,19 +5400,19 @@
         <v>539</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G68" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K68" s="15">
         <v>12</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M68" s="15">
         <v>1</v>
@@ -5421,7 +5421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" ht="18.75" customHeight="1">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>4</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D69" s="3">
         <f t="shared" si="4"/>
@@ -5440,19 +5440,19 @@
         <v>540</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G69" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K69" s="15">
         <v>12</v>
       </c>
       <c r="L69" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M69" s="15">
         <v>1</v>
@@ -5461,7 +5461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" ht="18.75" customHeight="1">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D70" s="3">
         <v>0</v>
@@ -5478,19 +5478,19 @@
         <v>256</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G70" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K70" s="15">
         <v>12</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M70" s="15">
         <v>1</v>
@@ -5499,7 +5499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" ht="18.75" customHeight="1">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
@@ -5516,19 +5516,19 @@
         <v>257</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G71" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K71" s="15">
         <v>12</v>
       </c>
       <c r="L71" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M71" s="15">
         <v>1</v>
@@ -5537,7 +5537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" ht="18.75" customHeight="1">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>5</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D72" s="3">
         <v>2</v>
@@ -5554,19 +5554,19 @@
         <v>258</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K72" s="15">
         <v>12</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M72" s="15">
         <v>1</v>
@@ -5575,7 +5575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="18.75" customHeight="1">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>6</v>
       </c>
       <c r="C73" s="27" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D73" s="3">
         <v>0</v>
@@ -5592,19 +5592,19 @@
         <v>61953</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K73" s="15">
         <v>12</v>
       </c>
       <c r="L73" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M73" s="15">
         <v>1</v>
@@ -5614,14 +5614,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X73" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="16">
-      <filters>
-        <filter val="demand"/>
-        <filter val="realtime"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:X73" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5849,45 +5842,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86A171EE-5F53-4D78-BFA7-825ADE5927F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4da14e33-fb1f-428b-aede-7872bd2aa051"/>
-    <ds:schemaRef ds:uri="87eaac2d-a5f8-4c7f-abd5-4f93f35bdb19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86A171EE-5F53-4D78-BFA7-825ADE5927F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE906B62-A8D9-443E-8C20-479E8ADBED59}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="4da14e33-fb1f-428b-aede-7872bd2aa051"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="87eaac2d-a5f8-4c7f-abd5-4f93f35bdb19"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE906B62-A8D9-443E-8C20-479E8ADBED59}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A639F79-A7CC-4E27-B001-C7904C814AE6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A639F79-A7CC-4E27-B001-C7904C814AE6}"/>
 </file>